--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_araucania.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_araucania.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>27.53923035299361</v>
+      </c>
+      <c r="C2">
         <v>25.63527177430478</v>
-      </c>
-      <c r="C2">
-        <v>27.53923035299361</v>
       </c>
       <c r="D2">
         <v>3.90087535955963</v>
       </c>
       <c r="E2">
-        <v>16.73599157710996</v>
+        <v>17.97899126194426</v>
       </c>
       <c r="F2">
         <v>65.28501716094577</v>
       </c>
       <c r="G2">
-        <v>17.97899126194426</v>
+        <v>16.73599157710996</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>33.8698904621961</v>
+      </c>
+      <c r="C3">
         <v>36.32113278119156</v>
-      </c>
-      <c r="C3">
-        <v>33.8698904621961</v>
       </c>
       <c r="D3">
         <v>2.753218094887826</v>
       </c>
       <c r="E3">
-        <v>21.34139162513245</v>
+        <v>19.90110278246537</v>
       </c>
       <c r="F3">
         <v>58.75750559240218</v>
       </c>
       <c r="G3">
-        <v>19.90110278246537</v>
+        <v>21.34139162513245</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>32.29157006398961</v>
+      </c>
+      <c r="C4">
         <v>42.21459705091348</v>
-      </c>
-      <c r="C4">
-        <v>32.29157006398961</v>
       </c>
       <c r="D4">
         <v>2.368848857644991</v>
       </c>
       <c r="E4">
-        <v>24.19089121539034</v>
+        <v>18.504543763618</v>
       </c>
       <c r="F4">
         <v>57.30456502099165</v>
       </c>
       <c r="G4">
-        <v>18.504543763618</v>
+        <v>24.19089121539034</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>34.79661699556987</v>
+      </c>
+      <c r="C5">
         <v>31.47402335884011</v>
-      </c>
-      <c r="C5">
-        <v>34.79661699556987</v>
       </c>
       <c r="D5">
         <v>3.177223288547665</v>
       </c>
       <c r="E5">
-        <v>18.92939324209761</v>
+        <v>20.92769771103306</v>
       </c>
       <c r="F5">
         <v>60.14290904686933</v>
       </c>
       <c r="G5">
-        <v>20.92769771103306</v>
+        <v>18.92939324209761</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>27.97353942887084</v>
+      </c>
+      <c r="C6">
         <v>34.93581346607284</v>
-      </c>
-      <c r="C6">
-        <v>27.97353942887084</v>
       </c>
       <c r="D6">
         <v>2.862392200974878</v>
       </c>
       <c r="E6">
-        <v>21.44494029670728</v>
+        <v>17.17122984762594</v>
       </c>
       <c r="F6">
         <v>61.38382985566678</v>
       </c>
       <c r="G6">
-        <v>17.17122984762594</v>
+        <v>21.44494029670728</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>34.48650115316782</v>
+      </c>
+      <c r="C7">
         <v>34.28300094966762</v>
-      </c>
-      <c r="C7">
-        <v>34.48650115316782</v>
       </c>
       <c r="D7">
         <v>2.916897506925208</v>
       </c>
       <c r="E7">
-        <v>20.31350482315113</v>
+        <v>20.43408360128618</v>
       </c>
       <c r="F7">
         <v>59.25241157556271</v>
       </c>
       <c r="G7">
-        <v>20.43408360128618</v>
+        <v>20.31350482315113</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.54298041818785</v>
+      </c>
+      <c r="C8">
         <v>38.99767673415201</v>
-      </c>
-      <c r="C8">
-        <v>28.54298041818785</v>
       </c>
       <c r="D8">
         <v>2.564255319148936</v>
       </c>
       <c r="E8">
-        <v>23.27654516640254</v>
+        <v>17.0364500792393</v>
       </c>
       <c r="F8">
         <v>59.68700475435816</v>
       </c>
       <c r="G8">
-        <v>17.0364500792393</v>
+        <v>23.27654516640254</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>32.24452626994497</v>
+      </c>
+      <c r="C9">
         <v>27.71904818466168</v>
-      </c>
-      <c r="C9">
-        <v>32.24452626994497</v>
       </c>
       <c r="D9">
         <v>3.607627481788316</v>
       </c>
       <c r="E9">
-        <v>17.32835008167912</v>
+        <v>20.15741794960646</v>
       </c>
       <c r="F9">
         <v>62.51423196871441</v>
       </c>
       <c r="G9">
-        <v>20.15741794960646</v>
+        <v>17.32835008167912</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>30.27968630716913</v>
+      </c>
+      <c r="C10">
         <v>34.75605524325074</v>
-      </c>
-      <c r="C10">
-        <v>30.27968630716913</v>
       </c>
       <c r="D10">
         <v>2.877196485623003</v>
       </c>
       <c r="E10">
-        <v>21.05971404541632</v>
+        <v>18.34735071488646</v>
       </c>
       <c r="F10">
         <v>60.59293523969723</v>
       </c>
       <c r="G10">
-        <v>18.34735071488646</v>
+        <v>21.05971404541632</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>33.07473493664339</v>
+      </c>
+      <c r="C11">
         <v>42.33255753814326</v>
-      </c>
-      <c r="C11">
-        <v>33.07473493664339</v>
       </c>
       <c r="D11">
         <v>2.362248014660965</v>
       </c>
       <c r="E11">
-        <v>24.13386407194457</v>
+        <v>18.85596343800678</v>
       </c>
       <c r="F11">
         <v>57.01017249004866</v>
       </c>
       <c r="G11">
-        <v>18.85596343800678</v>
+        <v>24.13386407194457</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.88963531669866</v>
+      </c>
+      <c r="C12">
         <v>34.00671785028791</v>
-      </c>
-      <c r="C12">
-        <v>29.88963531669866</v>
       </c>
       <c r="D12">
         <v>2.940595456469592</v>
       </c>
       <c r="E12">
-        <v>20.74891673498068</v>
+        <v>18.23691298746926</v>
       </c>
       <c r="F12">
         <v>61.01417027755006</v>
       </c>
       <c r="G12">
-        <v>18.23691298746926</v>
+        <v>20.74891673498068</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>31.51126722951459</v>
+      </c>
+      <c r="C13">
         <v>24.29489944742302</v>
-      </c>
-      <c r="C13">
-        <v>31.51126722951459</v>
       </c>
       <c r="D13">
         <v>4.116090301851695</v>
       </c>
       <c r="E13">
-        <v>15.59302816158633</v>
+        <v>20.2246598460078</v>
       </c>
       <c r="F13">
         <v>64.18231199240587</v>
       </c>
       <c r="G13">
-        <v>20.2246598460078</v>
+        <v>15.59302816158633</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>32.94930875576037</v>
+      </c>
+      <c r="C14">
         <v>31.88940092165898</v>
-      </c>
-      <c r="C14">
-        <v>32.94930875576037</v>
       </c>
       <c r="D14">
         <v>3.135838150289017</v>
       </c>
       <c r="E14">
-        <v>19.34582051998881</v>
+        <v>19.98881744478614</v>
       </c>
       <c r="F14">
         <v>60.66536203522504</v>
       </c>
       <c r="G14">
-        <v>19.98881744478614</v>
+        <v>19.34582051998881</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>29.8888036809816</v>
+      </c>
+      <c r="C15">
         <v>34.60506134969325</v>
-      </c>
-      <c r="C15">
-        <v>29.8888036809816</v>
       </c>
       <c r="D15">
         <v>2.889750692520776</v>
       </c>
       <c r="E15">
-        <v>21.03729603729604</v>
+        <v>18.17016317016317</v>
       </c>
       <c r="F15">
         <v>60.7925407925408</v>
       </c>
       <c r="G15">
-        <v>18.17016317016317</v>
+        <v>21.03729603729604</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>31.18784668432362</v>
+      </c>
+      <c r="C16">
         <v>23.76692818949578</v>
-      </c>
-      <c r="C16">
-        <v>31.18784668432362</v>
       </c>
       <c r="D16">
         <v>4.207527333894029</v>
       </c>
       <c r="E16">
-        <v>15.33797729618163</v>
+        <v>20.12706398348813</v>
       </c>
       <c r="F16">
         <v>64.53495872033022</v>
       </c>
       <c r="G16">
-        <v>20.12706398348813</v>
+        <v>15.33797729618163</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>33.87118829481745</v>
+      </c>
+      <c r="C17">
         <v>39.40927116094626</v>
-      </c>
-      <c r="C17">
-        <v>33.87118829481745</v>
       </c>
       <c r="D17">
         <v>2.537473976405274</v>
       </c>
       <c r="E17">
-        <v>22.74305555555555</v>
+        <v>19.54703282828283</v>
       </c>
       <c r="F17">
         <v>57.70991161616161</v>
       </c>
       <c r="G17">
-        <v>19.54703282828283</v>
+        <v>22.74305555555555</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>32.3589626933576</v>
+      </c>
+      <c r="C18">
         <v>40.10464058234759</v>
-      </c>
-      <c r="C18">
-        <v>32.3589626933576</v>
       </c>
       <c r="D18">
         <v>2.493477027793534</v>
       </c>
       <c r="E18">
-        <v>23.25397348809602</v>
+        <v>18.76277781441667</v>
       </c>
       <c r="F18">
         <v>57.9832486974873</v>
       </c>
       <c r="G18">
-        <v>18.76277781441667</v>
+        <v>23.25397348809602</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>29.49400798934754</v>
+      </c>
+      <c r="C19">
         <v>37.71637816245006</v>
-      </c>
-      <c r="C19">
-        <v>29.49400798934754</v>
       </c>
       <c r="D19">
         <v>2.651368049426302</v>
       </c>
       <c r="E19">
-        <v>22.5562412900657</v>
+        <v>17.6388612383038</v>
       </c>
       <c r="F19">
-        <v>59.8048974716305</v>
+        <v>59.80489747163049</v>
       </c>
       <c r="G19">
-        <v>17.6388612383038</v>
+        <v>22.55624129006569</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>32.56430505415162</v>
+      </c>
+      <c r="C20">
         <v>28.23217509025271</v>
-      </c>
-      <c r="C20">
-        <v>32.56430505415162</v>
       </c>
       <c r="D20">
         <v>3.542057942057942</v>
       </c>
       <c r="E20">
+        <v>20.25187679786712</v>
+      </c>
+      <c r="F20">
+        <v>62.19041605276083</v>
+      </c>
+      <c r="G20">
         <v>17.55770714937206</v>
-      </c>
-      <c r="F20">
-        <v>62.19041605276082</v>
-      </c>
-      <c r="G20">
-        <v>20.25187679786711</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>32.31537330832784</v>
+      </c>
+      <c r="C21">
         <v>28.55948096710426</v>
-      </c>
-      <c r="C21">
-        <v>32.31537330832784</v>
       </c>
       <c r="D21">
         <v>3.501464193806016</v>
       </c>
       <c r="E21">
-        <v>17.75260720249535</v>
+        <v>20.08727433126437</v>
       </c>
       <c r="F21">
         <v>62.16011846624027</v>
       </c>
       <c r="G21">
-        <v>20.08727433126437</v>
+        <v>17.75260720249535</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>37.5507835171213</v>
+      </c>
+      <c r="C22">
         <v>32.29831688914684</v>
-      </c>
-      <c r="C22">
-        <v>37.5507835171213</v>
       </c>
       <c r="D22">
         <v>3.096136567834681</v>
       </c>
       <c r="E22">
+        <v>22.10832051939176</v>
+      </c>
+      <c r="F22">
+        <v>58.87579019306338</v>
+      </c>
+      <c r="G22">
         <v>19.01588928754485</v>
-      </c>
-      <c r="F22">
-        <v>58.87579019306339</v>
-      </c>
-      <c r="G22">
-        <v>22.10832051939177</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>30.26839244690985</v>
+      </c>
+      <c r="C23">
         <v>29.72208214265703</v>
-      </c>
-      <c r="C23">
-        <v>30.26839244690985</v>
       </c>
       <c r="D23">
         <v>3.364501838062023</v>
       </c>
       <c r="E23">
-        <v>18.57740732309524</v>
+        <v>18.91887159192393</v>
       </c>
       <c r="F23">
         <v>62.50372108498082</v>
       </c>
       <c r="G23">
-        <v>18.91887159192393</v>
+        <v>18.57740732309524</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>32.4094742063492</v>
+      </c>
+      <c r="C24">
         <v>29.53249007936508</v>
-      </c>
-      <c r="C24">
-        <v>32.4094742063492</v>
       </c>
       <c r="D24">
         <v>3.386101196724753</v>
       </c>
       <c r="E24">
+        <v>20.01301784210123</v>
+      </c>
+      <c r="F24">
+        <v>61.75051688490695</v>
+      </c>
+      <c r="G24">
         <v>18.23646527299181</v>
-      </c>
-      <c r="F24">
-        <v>61.75051688490696</v>
-      </c>
-      <c r="G24">
-        <v>20.01301784210123</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>31.30620190970613</v>
+      </c>
+      <c r="C25">
         <v>39.88133864837305</v>
-      </c>
-      <c r="C25">
-        <v>31.30620190970613</v>
       </c>
       <c r="D25">
         <v>2.50743840074384</v>
       </c>
       <c r="E25">
+        <v>18.28766381457815</v>
+      </c>
+      <c r="F25">
+        <v>58.41546626231995</v>
+      </c>
+      <c r="G25">
         <v>23.29686992310192</v>
-      </c>
-      <c r="F25">
-        <v>58.41546626231994</v>
-      </c>
-      <c r="G25">
-        <v>18.28766381457814</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>38.22784810126582</v>
+      </c>
+      <c r="C26">
         <v>31.31450827653359</v>
-      </c>
-      <c r="C26">
-        <v>38.22784810126582</v>
       </c>
       <c r="D26">
         <v>3.193407960199005</v>
       </c>
       <c r="E26">
+        <v>22.54766827475305</v>
+      </c>
+      <c r="F26">
+        <v>58.98231104985069</v>
+      </c>
+      <c r="G26">
         <v>18.47002067539628</v>
-      </c>
-      <c r="F26">
-        <v>58.98231104985067</v>
-      </c>
-      <c r="G26">
-        <v>22.54766827475304</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>34.20489296636086</v>
+      </c>
+      <c r="C27">
         <v>31.95718654434251</v>
-      </c>
-      <c r="C27">
-        <v>34.20489296636086</v>
       </c>
       <c r="D27">
         <v>3.129186602870814</v>
       </c>
       <c r="E27">
-        <v>19.23253887917549</v>
+        <v>20.58525812091654</v>
       </c>
       <c r="F27">
         <v>60.18220299990798</v>
       </c>
       <c r="G27">
-        <v>20.58525812091654</v>
+        <v>19.23253887917549</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>31.23414071510957</v>
+      </c>
+      <c r="C28">
         <v>37.11649365628604</v>
-      </c>
-      <c r="C28">
-        <v>31.23414071510957</v>
       </c>
       <c r="D28">
         <v>2.694220012430081</v>
       </c>
       <c r="E28">
-        <v>22.0471362016991</v>
+        <v>18.55302822691148</v>
       </c>
       <c r="F28">
         <v>59.39983557138943</v>
       </c>
       <c r="G28">
-        <v>18.55302822691148</v>
+        <v>22.0471362016991</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>31.21827411167513</v>
+      </c>
+      <c r="C29">
         <v>34.40899202320522</v>
-      </c>
-      <c r="C29">
-        <v>31.21827411167513</v>
       </c>
       <c r="D29">
         <v>2.906217070600632</v>
       </c>
       <c r="E29">
-        <v>20.77495621716287</v>
+        <v>18.84851138353765</v>
       </c>
       <c r="F29">
         <v>60.37653239929947</v>
       </c>
       <c r="G29">
-        <v>18.84851138353765</v>
+        <v>20.77495621716287</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>32.48132127408573</v>
+      </c>
+      <c r="C30">
         <v>35.33883864202386</v>
-      </c>
-      <c r="C30">
-        <v>32.48132127408573</v>
       </c>
       <c r="D30">
         <v>2.829747774480712</v>
       </c>
       <c r="E30">
-        <v>21.05756463328907</v>
+        <v>19.35483870967742</v>
       </c>
       <c r="F30">
         <v>59.58759665703351</v>
       </c>
       <c r="G30">
-        <v>19.35483870967742</v>
+        <v>21.05756463328907</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>32.78135541245017</v>
+      </c>
+      <c r="C31">
         <v>30.22079116835327</v>
-      </c>
-      <c r="C31">
-        <v>32.78135541245017</v>
       </c>
       <c r="D31">
         <v>3.308980213089802</v>
       </c>
       <c r="E31">
+        <v>20.11099614335434</v>
+      </c>
+      <c r="F31">
+        <v>61.34888533534004</v>
+      </c>
+      <c r="G31">
         <v>18.54011852130562</v>
-      </c>
-      <c r="F31">
-        <v>61.34888533534005</v>
-      </c>
-      <c r="G31">
-        <v>20.11099614335434</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>32.19950801594707</v>
+      </c>
+      <c r="C32">
         <v>37.42471795741793</v>
-      </c>
-      <c r="C32">
-        <v>32.19950801594707</v>
       </c>
       <c r="D32">
         <v>2.672030825022666</v>
       </c>
       <c r="E32">
-        <v>22.06330949642447</v>
+        <v>18.98284742711407</v>
       </c>
       <c r="F32">
         <v>58.95384307646147</v>
       </c>
       <c r="G32">
-        <v>18.98284742711407</v>
+        <v>22.06330949642447</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>28.61714285714286</v>
+      </c>
+      <c r="C33">
         <v>33.63657142857143</v>
-      </c>
-      <c r="C33">
-        <v>28.61714285714286</v>
       </c>
       <c r="D33">
         <v>2.972954607230226</v>
       </c>
       <c r="E33">
-        <v>20.73084833629166</v>
+        <v>17.63728059053898</v>
       </c>
       <c r="F33">
         <v>61.63187107316936</v>
       </c>
       <c r="G33">
-        <v>17.63728059053898</v>
+        <v>20.73084833629166</v>
       </c>
     </row>
   </sheetData>
